--- a/data/GDP_VNM.xlsx
+++ b/data/GDP_VNM.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\GSO-chung\Tuấn Anh\excel chung\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\PC-Ngan\1. Contents\1.Work\A.Vụ TKQG\2. Cungcapsolieu-Gopy\7. e-GDDS\e-\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -23,12 +23,12 @@
   <definedNames>
     <definedName name="Reporting_Currency_Code">'[1]Report Form'!$S$16</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="380">
   <si>
     <t>DATA_DOMAIN</t>
   </si>
@@ -1217,11 +1217,14 @@
   <si>
     <t>Ghi chú: Số liệu từ năm 2025 là số liệu tính theo giá so sánh năm 2020</t>
   </si>
+  <si>
+    <t>2026-Q2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -1787,9 +1790,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="18" applyFont="1"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Comma" xfId="18" builtinId="3"/>
@@ -27653,7 +27654,9 @@
     <col min="3" max="3" width="31.140625" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="64.7109375" customWidth="1"/>
     <col min="5" max="6" width="9.140625" style="22"/>
-    <col min="7" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:127 16079:16080" s="1" customFormat="1" ht="14.25" hidden="1" customHeight="1">
@@ -27786,7 +27789,10 @@
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" spans="1:127 16079:16080" ht="14.25" customHeight="1" thickBot="1"/>
+    <row r="9" spans="1:127 16079:16080" ht="14.25" customHeight="1" thickBot="1">
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+    </row>
     <row r="10" spans="1:127 16079:16080" s="11" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="A10" s="18" t="s">
         <v>7</v>
@@ -27821,7 +27827,9 @@
       <c r="K10" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="L10" s="10"/>
+      <c r="L10" s="10" t="s">
+        <v>379</v>
+      </c>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
@@ -27954,7 +27962,7 @@
       <c r="I11" s="94"/>
       <c r="J11" s="94"/>
       <c r="K11" s="94"/>
-      <c r="L11" s="16"/>
+      <c r="L11" s="94"/>
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
       <c r="O11" s="16"/>
@@ -28009,15 +28017,18 @@
         <v>14</v>
       </c>
       <c r="G12" s="34">
-        <f t="shared" ref="G12" si="0">+G13+G17+G24+G39</f>
         <v>2817538.2943781861</v>
       </c>
-      <c r="H12" s="34"/>
+      <c r="H12" s="34">
+        <v>3082031.2927191658</v>
+      </c>
       <c r="I12" s="34"/>
       <c r="J12" s="34"/>
       <c r="K12" s="34">
-        <f t="shared" ref="K12" si="1">+K13+K17+K24+K39</f>
-        <v>3142295.8659095448</v>
+        <v>3143977.9418364973</v>
+      </c>
+      <c r="L12">
+        <v>3479487.2309509148</v>
       </c>
     </row>
     <row r="13" spans="1:127 16079:16080" s="27" customFormat="1">
@@ -28040,15 +28051,18 @@
         <v>14</v>
       </c>
       <c r="G13" s="59">
-        <f t="shared" ref="G13" si="2">+G14+G15+G16</f>
         <v>324173.27900568419</v>
       </c>
-      <c r="H13" s="59"/>
+      <c r="H13" s="59">
+        <v>341074.01264721953</v>
+      </c>
       <c r="I13" s="59"/>
       <c r="J13" s="59"/>
       <c r="K13" s="59">
-        <f t="shared" ref="K13" si="3">+K14+K15+K16</f>
-        <v>342159.90231610107</v>
+        <v>343185.9003769721</v>
+      </c>
+      <c r="L13" s="27">
+        <v>359605.36965954851</v>
       </c>
     </row>
     <row r="14" spans="1:127 16079:16080">
@@ -28073,11 +28087,16 @@
       <c r="G14" s="32">
         <v>251283.14907296048</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="32">
+        <v>244381.8386302244</v>
+      </c>
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
       <c r="K14" s="32">
-        <v>263046.2762050085</v>
+        <v>263927.77566804813</v>
+      </c>
+      <c r="L14" s="32">
+        <v>252667.11721023294</v>
       </c>
     </row>
     <row r="15" spans="1:127 16079:16080">
@@ -28102,11 +28121,16 @@
       <c r="G15" s="32">
         <v>12187.202758070518</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="32">
+        <v>17618.207148647445</v>
+      </c>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
       <c r="K15" s="32">
-        <v>12938.527020487076</v>
+        <v>12937.533064332383</v>
+      </c>
+      <c r="L15" s="32">
+        <v>20005.104520353212</v>
       </c>
     </row>
     <row r="16" spans="1:127 16079:16080">
@@ -28131,14 +28155,19 @@
       <c r="G16" s="32">
         <v>60702.927174653189</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="32">
+        <v>79073.966868347663</v>
+      </c>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
       <c r="K16" s="32">
-        <v>66175.099090605494</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="27" customFormat="1">
+        <v>66320.591644591594</v>
+      </c>
+      <c r="L16" s="32">
+        <v>86933.147928962338</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="27" customFormat="1">
       <c r="A17" s="27" t="s">
         <v>248</v>
       </c>
@@ -28158,18 +28187,21 @@
         <v>14</v>
       </c>
       <c r="G17" s="59">
-        <f t="shared" ref="G17" si="4">+G18+G23</f>
         <v>1028416.9264223459</v>
       </c>
-      <c r="H17" s="59"/>
+      <c r="H17" s="59">
+        <v>1143790.6882995788</v>
+      </c>
       <c r="I17" s="59"/>
       <c r="J17" s="59"/>
       <c r="K17" s="59">
-        <f t="shared" ref="K17" si="5">+K18+K23</f>
-        <v>1167284.9627485878</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>1166069.4196260029</v>
+      </c>
+      <c r="L17" s="34">
+        <v>1328412.3798630654</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>249</v>
       </c>
@@ -28189,18 +28221,21 @@
         <v>14</v>
       </c>
       <c r="G18" s="30">
-        <f t="shared" ref="G18" si="6">+G19+G20+G21+G22</f>
         <v>890294.51390288654</v>
       </c>
-      <c r="H18" s="30"/>
+      <c r="H18" s="30">
+        <v>962238.95817525859</v>
+      </c>
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
       <c r="K18" s="30">
-        <f t="shared" ref="K18" si="7">+K19+K20+K21+K22</f>
-        <v>1008603.1876857104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>1006910.504334641</v>
+      </c>
+      <c r="L18" s="32">
+        <v>1113691.7946914625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -28222,14 +28257,19 @@
       <c r="G19" s="32">
         <v>72323.879618650011</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="32">
+        <v>67765.742481202469</v>
+      </c>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
       <c r="K19" s="32">
-        <v>84319.44172125998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>79784.971643917757</v>
+      </c>
+      <c r="L19" s="32">
+        <v>79622.081088534484</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -28251,14 +28291,19 @@
       <c r="G20" s="32">
         <v>671029.34466926812</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="32">
+        <v>739754.38718272292</v>
+      </c>
       <c r="I20" s="32"/>
       <c r="J20" s="32"/>
       <c r="K20" s="32">
-        <v>760494.64429575007</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>764711.23286274122</v>
+      </c>
+      <c r="L20" s="32">
+        <v>847823.017595849</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -28280,14 +28325,19 @@
       <c r="G21" s="32">
         <v>133093.53655650845</v>
       </c>
-      <c r="H21" s="32"/>
+      <c r="H21" s="32">
+        <v>139588.30367456924</v>
+      </c>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
       <c r="K21" s="32">
-        <v>148603.35394720238</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>147057.16813695268</v>
+      </c>
+      <c r="L21" s="32">
+        <v>169510.15340599354</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -28309,14 +28359,19 @@
       <c r="G22" s="32">
         <v>13847.753058460128</v>
       </c>
-      <c r="H22" s="32"/>
+      <c r="H22" s="32">
+        <v>15130.524836763923</v>
+      </c>
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
       <c r="K22" s="32">
-        <v>15185.747721497855</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>15357.131691029455</v>
+      </c>
+      <c r="L22" s="32">
+        <v>16736.542601085526</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -28338,14 +28393,19 @@
       <c r="G23" s="32">
         <v>138122.41251945944</v>
       </c>
-      <c r="H23" s="32"/>
+      <c r="H23" s="32">
+        <v>181551.73012432017</v>
+      </c>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
       <c r="K23" s="32">
-        <v>158681.77506287736</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>159158.91529136195</v>
+      </c>
+      <c r="L23" s="32">
+        <v>214720.58517160284</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
         <v>161</v>
       </c>
@@ -28365,18 +28425,21 @@
         <v>14</v>
       </c>
       <c r="G24" s="59">
-        <f t="shared" ref="G24" si="8">SUM(G25:G38)</f>
         <v>1222696.8309349152</v>
       </c>
-      <c r="H24" s="59"/>
+      <c r="H24" s="59">
+        <v>1349016.4115155863</v>
+      </c>
       <c r="I24" s="59"/>
       <c r="J24" s="59"/>
       <c r="K24" s="59">
-        <f t="shared" ref="K24" si="9">SUM(K25:K38)</f>
-        <v>1365455.1530024924</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>1366826.7739911582</v>
+      </c>
+      <c r="L24" s="32">
+        <v>1515880.7190211297</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -28398,14 +28461,19 @@
       <c r="G25" s="32">
         <v>297023.27543990716</v>
       </c>
-      <c r="H25" s="32"/>
+      <c r="H25" s="32">
+        <v>313964.77165378089</v>
+      </c>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
       <c r="K25" s="32">
-        <v>334305.90079864312</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>335354.35197795683</v>
+      </c>
+      <c r="L25" s="32">
+        <v>357190.25001365092</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -28427,14 +28495,19 @@
       <c r="G26" s="32">
         <v>157042.40703840583</v>
       </c>
-      <c r="H26" s="32"/>
+      <c r="H26" s="32">
+        <v>185887.24063108474</v>
+      </c>
       <c r="I26" s="32"/>
       <c r="J26" s="32"/>
       <c r="K26" s="32">
-        <v>177929.19086512172</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>176697.47539662835</v>
+      </c>
+      <c r="L26" s="32">
+        <v>221506.73456354599</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -28456,14 +28529,19 @@
       <c r="G27" s="32">
         <v>80759.497434867022</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="32">
+        <v>77290.806742002984</v>
+      </c>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
       <c r="K27" s="32">
-        <v>91654.687298188524</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>92404.443842779729</v>
+      </c>
+      <c r="L27" s="32">
+        <v>90272.052913504624</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -28485,14 +28563,19 @@
       <c r="G28" s="32">
         <v>96894.970861979775</v>
       </c>
-      <c r="H28" s="32"/>
+      <c r="H28" s="32">
+        <v>100128.06979683302</v>
+      </c>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
       <c r="K28" s="32">
-        <v>104311.57584947943</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>104985.48171554109</v>
+      </c>
+      <c r="L28" s="32">
+        <v>107872.5552172298</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
         <v>45</v>
       </c>
@@ -28514,14 +28597,19 @@
       <c r="G29" s="32">
         <v>132500.33883683122</v>
       </c>
-      <c r="H29" s="32"/>
+      <c r="H29" s="32">
+        <v>130169.16356384744</v>
+      </c>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
       <c r="K29" s="32">
-        <v>147576.69717584574</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>148048.28172592272</v>
+      </c>
+      <c r="L29" s="32">
+        <v>148002.23326297535</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -28543,14 +28631,19 @@
       <c r="G30" s="32">
         <v>95881.552000349038</v>
       </c>
-      <c r="H30" s="32"/>
+      <c r="H30" s="32">
+        <v>101727.62322506397</v>
+      </c>
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
       <c r="K30" s="32">
-        <v>107318.88634039115</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>107255.55715003528</v>
+      </c>
+      <c r="L30" s="32">
+        <v>112646.28643422532</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
         <v>47</v>
       </c>
@@ -28572,14 +28665,19 @@
       <c r="G31" s="32">
         <v>54129.295624783044</v>
       </c>
-      <c r="H31" s="32"/>
+      <c r="H31" s="32">
+        <v>63437.546690638119</v>
+      </c>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
       <c r="K31" s="32">
-        <v>60311.118081223241</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>59136.637594329848</v>
+      </c>
+      <c r="L31" s="32">
+        <v>69932.432223342301</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -28601,11 +28699,16 @@
       <c r="G32" s="32">
         <v>39413.571728543393</v>
       </c>
-      <c r="H32" s="32"/>
+      <c r="H32" s="32">
+        <v>42303.531600874252</v>
+      </c>
       <c r="I32" s="32"/>
       <c r="J32" s="32"/>
       <c r="K32" s="32">
-        <v>42889.958924544597</v>
+        <v>43343.17247624544</v>
+      </c>
+      <c r="L32" s="32">
+        <v>47936.696744771936</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -28630,12 +28733,17 @@
       <c r="G33" s="32">
         <v>50131.263610610433</v>
       </c>
-      <c r="H33" s="32"/>
+      <c r="H33" s="32">
+        <v>67263.049588210008</v>
+      </c>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
       <c r="K33" s="32">
         <v>56833.314247963492</v>
       </c>
+      <c r="L33" s="32">
+        <v>64020.117255730474</v>
+      </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" t="s">
@@ -28659,12 +28767,17 @@
       <c r="G34" s="32">
         <v>103432.82534225985</v>
       </c>
-      <c r="H34" s="32"/>
+      <c r="H34" s="32">
+        <v>126500.70257099105</v>
+      </c>
       <c r="I34" s="32"/>
       <c r="J34" s="32"/>
       <c r="K34" s="32">
         <v>115793.04797065991</v>
       </c>
+      <c r="L34" s="32">
+        <v>141063.31283835563</v>
+      </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" t="s">
@@ -28688,11 +28801,16 @@
       <c r="G35" s="32">
         <v>71646.418174467733</v>
       </c>
-      <c r="H35" s="32"/>
+      <c r="H35" s="32">
+        <v>94521.136123444128</v>
+      </c>
       <c r="I35" s="32"/>
       <c r="J35" s="32"/>
       <c r="K35" s="32">
-        <v>77075.141458894519</v>
+        <v>77396.775663384426</v>
+      </c>
+      <c r="L35" s="32">
+        <v>103282.19297349149</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -28717,11 +28835,16 @@
       <c r="G36" s="32">
         <v>18820.749604145858</v>
       </c>
-      <c r="H36" s="32"/>
+      <c r="H36" s="32">
+        <v>19369.786270882458</v>
+      </c>
       <c r="I36" s="32"/>
       <c r="J36" s="32"/>
       <c r="K36" s="32">
-        <v>21069.951838933721</v>
+        <v>21063.49080260711</v>
+      </c>
+      <c r="L36" s="32">
+        <v>21806.507931285163</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -28746,11 +28869,16 @@
       <c r="G37" s="32">
         <v>21259.790893747358</v>
       </c>
-      <c r="H37" s="32"/>
+      <c r="H37" s="32">
+        <v>22588.528473661328</v>
+      </c>
       <c r="I37" s="32"/>
       <c r="J37" s="32"/>
       <c r="K37" s="32">
-        <v>23946.461579881263</v>
+        <v>24075.522854382092</v>
+      </c>
+      <c r="L37" s="32">
+        <v>25886.882895678602</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="60">
@@ -28775,11 +28903,16 @@
       <c r="G38" s="32">
         <v>3760.8743440176677</v>
       </c>
-      <c r="H38" s="32"/>
+      <c r="H38" s="32">
+        <v>3864.4545842719053</v>
+      </c>
       <c r="I38" s="32"/>
       <c r="J38" s="32"/>
       <c r="K38" s="32">
-        <v>4439.220572722008</v>
+        <v>4439.2205727220107</v>
+      </c>
+      <c r="L38" s="32">
+        <v>4462.4637533424784</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -28804,11 +28937,16 @@
       <c r="G39" s="32">
         <v>242251.25801524118</v>
       </c>
-      <c r="H39" s="32"/>
+      <c r="H39" s="32">
+        <v>248150.18025678099</v>
+      </c>
       <c r="I39" s="32"/>
       <c r="J39" s="32"/>
       <c r="K39" s="32">
-        <v>267395.84784236364</v>
+        <v>267895.84784236399</v>
+      </c>
+      <c r="L39" s="32">
+        <v>275588.76240717102</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="75" customFormat="1">
@@ -28838,18 +28976,23 @@
         <v>16</v>
       </c>
       <c r="F41" s="33">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="G41" s="34">
-        <f t="shared" ref="G41" si="10">+G42+G46+G53+G68</f>
         <v>2401936.873780326</v>
       </c>
-      <c r="H41" s="34"/>
+      <c r="H41" s="34">
+        <v>2633501.7144493875</v>
+      </c>
       <c r="I41" s="34"/>
       <c r="J41" s="34"/>
       <c r="K41" s="34">
-        <f t="shared" ref="K41" si="11">+K42+K46+K53+K68</f>
-        <v>2589918.33923019</v>
+        <f t="shared" ref="K41:L41" si="0">+K42+K46+K53+K68</f>
+        <v>2592640.1663886518</v>
+      </c>
+      <c r="L41" s="34">
+        <f t="shared" si="0"/>
+        <v>2854515.4598837672</v>
       </c>
       <c r="M41" s="97"/>
     </row>
@@ -28870,18 +29013,23 @@
         <v>16</v>
       </c>
       <c r="F42" s="33">
-        <v>2020</v>
-      </c>
-      <c r="G42" s="34">
-        <f t="shared" ref="G42" si="12">+G43+G44+G45</f>
+        <v>2010</v>
+      </c>
+      <c r="G42" s="59">
         <v>270632.85587437393</v>
       </c>
-      <c r="H42" s="34"/>
+      <c r="H42" s="59">
+        <v>286055.56141180696</v>
+      </c>
       <c r="I42" s="34"/>
       <c r="J42" s="34"/>
       <c r="K42" s="34">
-        <f t="shared" ref="K42" si="13">+K43+K44+K45</f>
-        <v>280313.9775046474</v>
+        <f t="shared" ref="K42:L42" si="1">+K43+K44+K45</f>
+        <v>280587.27255974174</v>
+      </c>
+      <c r="L42" s="34">
+        <f t="shared" si="1"/>
+        <v>297670.74211896921</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -28900,17 +29048,22 @@
       <c r="E43" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F43" s="99">
-        <v>2020</v>
+      <c r="F43" s="22">
+        <v>2010</v>
       </c>
       <c r="G43" s="32">
         <v>206490.94674740109</v>
       </c>
-      <c r="H43" s="32"/>
+      <c r="H43" s="32">
+        <v>202539.92824544391</v>
+      </c>
       <c r="I43" s="32"/>
       <c r="J43" s="32"/>
       <c r="K43" s="32">
-        <v>213424.52811061262</v>
+        <v>213572.72344038161</v>
+      </c>
+      <c r="L43" s="32">
+        <v>210053.76758496641</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -28929,17 +29082,22 @@
       <c r="E44" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="99">
-        <v>2020</v>
+      <c r="F44" s="22">
+        <v>2010</v>
       </c>
       <c r="G44" s="32">
         <v>11440.616132244975</v>
       </c>
-      <c r="H44" s="32"/>
+      <c r="H44" s="32">
+        <v>14866.458964063977</v>
+      </c>
       <c r="I44" s="32"/>
       <c r="J44" s="32"/>
       <c r="K44" s="32">
-        <v>11809.00326332139</v>
+        <v>11807.024530739849</v>
+      </c>
+      <c r="L44" s="32">
+        <v>15547.526110192854</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -28958,17 +29116,22 @@
       <c r="E45" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="99">
-        <v>2020</v>
+      <c r="F45" s="22">
+        <v>2010</v>
       </c>
       <c r="G45" s="32">
         <v>52701.29299472789</v>
       </c>
-      <c r="H45" s="32"/>
+      <c r="H45" s="32">
+        <v>68649.174202299051</v>
+      </c>
       <c r="I45" s="32"/>
       <c r="J45" s="32"/>
       <c r="K45" s="32">
-        <v>55080.446130713368</v>
+        <v>55207.524588620276</v>
+      </c>
+      <c r="L45" s="32">
+        <v>72069.448423809925</v>
       </c>
     </row>
     <row r="46" spans="1:13" s="27" customFormat="1">
@@ -28988,18 +29151,23 @@
         <v>16</v>
       </c>
       <c r="F46" s="33">
-        <v>2020</v>
-      </c>
-      <c r="G46" s="34">
-        <f t="shared" ref="G46" si="14">+G47+G52</f>
+        <v>2010</v>
+      </c>
+      <c r="G46" s="59">
         <v>854064.79716577614</v>
       </c>
-      <c r="H46" s="34"/>
+      <c r="H46" s="59">
+        <v>978866.25379722426</v>
+      </c>
       <c r="I46" s="34"/>
       <c r="J46" s="34"/>
       <c r="K46" s="34">
-        <f t="shared" ref="K46" si="15">+K47+K52</f>
-        <v>930262.75606648333</v>
+        <f t="shared" ref="K46:L46" si="2">+K47+K52</f>
+        <v>931017.25741258624</v>
+      </c>
+      <c r="L46" s="34">
+        <f t="shared" si="2"/>
+        <v>1081721.402653893</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -29018,19 +29186,24 @@
       <c r="E47" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F47" s="99">
-        <v>2020</v>
-      </c>
-      <c r="G47" s="32">
-        <f t="shared" ref="G47" si="16">+G48+G49+G50+G51</f>
+      <c r="F47" s="22">
+        <v>2010</v>
+      </c>
+      <c r="G47" s="30">
         <v>735406.7138695328</v>
       </c>
-      <c r="H47" s="32"/>
+      <c r="H47" s="30">
+        <v>823208.18691571895</v>
+      </c>
       <c r="I47" s="32"/>
       <c r="J47" s="32"/>
       <c r="K47" s="32">
-        <f t="shared" ref="K47" si="17">+K48+K49+K50+K51</f>
-        <v>801680.81977304234</v>
+        <f t="shared" ref="K47:L47" si="3">+K48+K49+K50+K51</f>
+        <v>802266.93871478294</v>
+      </c>
+      <c r="L47" s="32">
+        <f t="shared" si="3"/>
+        <v>910061.81788118393</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -29049,20 +29222,25 @@
       <c r="E48" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F48" s="99">
-        <v>2020</v>
+      <c r="F48" s="22">
+        <v>2010</v>
       </c>
       <c r="G48" s="32">
         <v>45034.862010526485</v>
       </c>
-      <c r="H48" s="32"/>
+      <c r="H48" s="32">
+        <v>46456.765921094302</v>
+      </c>
       <c r="I48" s="32"/>
       <c r="J48" s="32"/>
       <c r="K48" s="32">
-        <v>47476.279622914662</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>47614.820044184351</v>
+      </c>
+      <c r="L48" s="32">
+        <v>49983.427383938266</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
         <v>58</v>
       </c>
@@ -29078,20 +29256,25 @@
       <c r="E49" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F49" s="99">
-        <v>2020</v>
+      <c r="F49" s="22">
+        <v>2010</v>
       </c>
       <c r="G49" s="32">
         <v>577764.48544014676</v>
       </c>
-      <c r="H49" s="32"/>
+      <c r="H49" s="32">
+        <v>653503.91921891924</v>
+      </c>
       <c r="I49" s="32"/>
       <c r="J49" s="32"/>
       <c r="K49" s="32">
-        <v>633977.13514077954</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>634747.81426375837</v>
+      </c>
+      <c r="L49" s="32">
+        <v>722522.85687510157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -29107,20 +29290,25 @@
       <c r="E50" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F50" s="99">
-        <v>2020</v>
+      <c r="F50" s="22">
+        <v>2010</v>
       </c>
       <c r="G50" s="32">
         <v>99993.613849551431</v>
       </c>
-      <c r="H50" s="32"/>
+      <c r="H50" s="32">
+        <v>109454.63217255163</v>
+      </c>
       <c r="I50" s="32"/>
       <c r="J50" s="32"/>
       <c r="K50" s="32">
-        <v>106531.30963425848</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+        <v>106223.212517404</v>
+      </c>
+      <c r="L50" s="32">
+        <v>122791.7814947681</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -29136,20 +29324,25 @@
       <c r="E51" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F51" s="99">
-        <v>2020</v>
+      <c r="F51" s="22">
+        <v>2010</v>
       </c>
       <c r="G51" s="32">
         <v>12613.752569308097</v>
       </c>
-      <c r="H51" s="32"/>
+      <c r="H51" s="32">
+        <v>13792.869603153738</v>
+      </c>
       <c r="I51" s="32"/>
       <c r="J51" s="32"/>
       <c r="K51" s="32">
-        <v>13696.095375089646</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>13681.091889436273</v>
+      </c>
+      <c r="L51" s="32">
+        <v>14763.752127376056</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
         <v>61</v>
       </c>
@@ -29165,20 +29358,25 @@
       <c r="E52" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F52" s="99">
-        <v>2020</v>
+      <c r="F52" s="22">
+        <v>2010</v>
       </c>
       <c r="G52" s="32">
         <v>118658.08329624332</v>
       </c>
-      <c r="H52" s="32"/>
+      <c r="H52" s="32">
+        <v>155658.06688150531</v>
+      </c>
       <c r="I52" s="32"/>
       <c r="J52" s="32"/>
       <c r="K52" s="32">
-        <v>128581.93629344103</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" s="27" customFormat="1">
+        <v>128750.31869780328</v>
+      </c>
+      <c r="L52" s="32">
+        <v>171659.58477270909</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="27" customFormat="1">
       <c r="A53" s="27" t="s">
         <v>164</v>
       </c>
@@ -29195,21 +29393,26 @@
         <v>16</v>
       </c>
       <c r="F53" s="33">
-        <v>2020</v>
-      </c>
-      <c r="G53" s="34">
-        <f t="shared" ref="G53" si="18">+SUM(G54:G67)</f>
+        <v>2010</v>
+      </c>
+      <c r="G53" s="59">
         <v>1063833.9704998196</v>
       </c>
-      <c r="H53" s="34"/>
+      <c r="H53" s="59">
+        <v>1155526.1732538703</v>
+      </c>
       <c r="I53" s="34"/>
       <c r="J53" s="34"/>
       <c r="K53" s="34">
-        <f t="shared" ref="K53" si="19">+SUM(K54:K67)</f>
-        <v>1150827.2637016862</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <f t="shared" ref="K53:L53" si="4">+SUM(K54:K67)</f>
+        <v>1152466.0744589509</v>
+      </c>
+      <c r="L53" s="34">
+        <f t="shared" si="4"/>
+        <v>1246492.8252070341</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -29225,20 +29428,25 @@
       <c r="E54" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F54" s="99">
-        <v>2020</v>
+      <c r="F54" s="22">
+        <v>2010</v>
       </c>
       <c r="G54" s="32">
         <v>261026.82773079208</v>
       </c>
-      <c r="H54" s="32"/>
+      <c r="H54" s="32">
+        <v>271117.35509681894</v>
+      </c>
       <c r="I54" s="32"/>
       <c r="J54" s="32"/>
       <c r="K54" s="32">
-        <v>286130.80760706577</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>286406.79769210547</v>
+      </c>
+      <c r="L54" s="32">
+        <v>297206.31492619397</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -29254,20 +29462,25 @@
       <c r="E55" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F55" s="99">
-        <v>2020</v>
+      <c r="F55" s="22">
+        <v>2010</v>
       </c>
       <c r="G55" s="32">
         <v>134221.11309231081</v>
       </c>
-      <c r="H55" s="32"/>
+      <c r="H55" s="32">
+        <v>154977.67147117425</v>
+      </c>
       <c r="I55" s="32"/>
       <c r="J55" s="32"/>
       <c r="K55" s="32">
-        <v>146231.76191062728</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>146336.92968135214</v>
+      </c>
+      <c r="L55" s="32">
+        <v>172312.49381548361</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -29283,20 +29496,25 @@
       <c r="E56" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F56" s="99">
-        <v>2020</v>
+      <c r="F56" s="22">
+        <v>2010</v>
       </c>
       <c r="G56" s="32">
         <v>66712.718309906122</v>
       </c>
-      <c r="H56" s="32"/>
+      <c r="H56" s="32">
+        <v>62386.576305657662</v>
+      </c>
       <c r="I56" s="32"/>
       <c r="J56" s="32"/>
       <c r="K56" s="32">
-        <v>71707.336323105977</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>71897.171976448662</v>
+      </c>
+      <c r="L56" s="32">
+        <v>67599.405563284992</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -29312,20 +29530,25 @@
       <c r="E57" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F57" s="99">
-        <v>2020</v>
+      <c r="F57" s="22">
+        <v>2010</v>
       </c>
       <c r="G57" s="32">
         <v>95108.689581268831</v>
       </c>
-      <c r="H57" s="32"/>
+      <c r="H57" s="32">
+        <v>96653.878319272189</v>
+      </c>
       <c r="I57" s="32"/>
       <c r="J57" s="32"/>
       <c r="K57" s="32">
-        <v>102383.91511431822</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>102481.1384992158</v>
+      </c>
+      <c r="L57" s="32">
+        <v>105095.80029984476</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -29341,20 +29564,25 @@
       <c r="E58" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F58" s="99">
-        <v>2020</v>
+      <c r="F58" s="22">
+        <v>2010</v>
       </c>
       <c r="G58" s="32">
         <v>114197.50102720056</v>
       </c>
-      <c r="H58" s="32"/>
+      <c r="H58" s="32">
+        <v>110996.59940311019</v>
+      </c>
       <c r="I58" s="32"/>
       <c r="J58" s="32"/>
       <c r="K58" s="32">
-        <v>122995.89038069166</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>123272.53796188271</v>
+      </c>
+      <c r="L58" s="32">
+        <v>119860.48855592459</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -29370,20 +29598,25 @@
       <c r="E59" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F59" s="99">
-        <v>2020</v>
+      <c r="F59" s="22">
+        <v>2010</v>
       </c>
       <c r="G59" s="32">
         <v>80995.208469539066</v>
       </c>
-      <c r="H59" s="32"/>
+      <c r="H59" s="32">
+        <v>83008.632282948209</v>
+      </c>
       <c r="I59" s="32"/>
       <c r="J59" s="32"/>
       <c r="K59" s="32">
-        <v>84810.10523941365</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>84755.071135933511</v>
+      </c>
+      <c r="L59" s="32">
+        <v>86903.641638685105</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -29399,20 +29632,25 @@
       <c r="E60" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F60" s="99">
-        <v>2020</v>
+      <c r="F60" s="22">
+        <v>2010</v>
       </c>
       <c r="G60" s="32">
         <v>51800.910277797579</v>
       </c>
-      <c r="H60" s="32"/>
+      <c r="H60" s="32">
+        <v>60599.0342418625</v>
+      </c>
       <c r="I60" s="32"/>
       <c r="J60" s="32"/>
       <c r="K60" s="32">
-        <v>55948.293646688966</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>55917.084166154076</v>
+      </c>
+      <c r="L60" s="32">
+        <v>65741.33843997345</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -29428,20 +29666,25 @@
       <c r="E61" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F61" s="99">
-        <v>2020</v>
+      <c r="F61" s="22">
+        <v>2010</v>
       </c>
       <c r="G61" s="32">
         <v>36320.462702611127</v>
       </c>
-      <c r="H61" s="32"/>
+      <c r="H61" s="32">
+        <v>40413.944056868277</v>
+      </c>
       <c r="I61" s="32"/>
       <c r="J61" s="32"/>
       <c r="K61" s="32">
-        <v>38886.105849610074</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>39231.952455004932</v>
+      </c>
+      <c r="L61" s="32">
+        <v>44403.482657715031</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -29457,20 +29700,25 @@
       <c r="E62" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F62" s="99">
-        <v>2020</v>
+      <c r="F62" s="22">
+        <v>2010</v>
       </c>
       <c r="G62" s="32">
         <v>45484.461360360292</v>
       </c>
-      <c r="H62" s="32"/>
+      <c r="H62" s="32">
+        <v>59705.195961830919</v>
+      </c>
       <c r="I62" s="32"/>
       <c r="J62" s="32"/>
       <c r="K62" s="32">
-        <v>49860.06654322696</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>49818.008592549122</v>
+      </c>
+      <c r="L62" s="32">
+        <v>53906.87281652871</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -29486,20 +29734,25 @@
       <c r="E63" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F63" s="99">
-        <v>2020</v>
+      <c r="F63" s="22">
+        <v>2010</v>
       </c>
       <c r="G63" s="32">
         <v>84776.552577609109</v>
       </c>
-      <c r="H63" s="32"/>
+      <c r="H63" s="32">
+        <v>103619.70566506</v>
+      </c>
       <c r="I63" s="32"/>
       <c r="J63" s="32"/>
       <c r="K63" s="32">
-        <v>91771.856596296755</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>91897.782994128283</v>
+      </c>
+      <c r="L63" s="32">
+        <v>111567.11368424397</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -29515,20 +29768,25 @@
       <c r="E64" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F64" s="99">
-        <v>2020</v>
+      <c r="F64" s="22">
+        <v>2010</v>
       </c>
       <c r="G64" s="32">
         <v>54684.973478863765</v>
       </c>
-      <c r="H64" s="32"/>
+      <c r="H64" s="32">
+        <v>71947.917343441542</v>
+      </c>
       <c r="I64" s="32"/>
       <c r="J64" s="32"/>
       <c r="K64" s="32">
-        <v>58459.584971065255</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>58666.402255403242</v>
+      </c>
+      <c r="L64" s="32">
+        <v>78042.137379247695</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -29544,20 +29802,25 @@
       <c r="E65" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F65" s="99">
-        <v>2020</v>
+      <c r="F65" s="22">
+        <v>2010</v>
       </c>
       <c r="G65" s="32">
         <v>17473.29654879959</v>
       </c>
-      <c r="H65" s="32"/>
+      <c r="H65" s="32">
+        <v>17840.111557989683</v>
+      </c>
       <c r="I65" s="32"/>
       <c r="J65" s="32"/>
       <c r="K65" s="32">
-        <v>19170.987090881885</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+        <v>19170.654722152911</v>
+      </c>
+      <c r="L65" s="32">
+        <v>19711.671181370068</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -29573,20 +29836,25 @@
       <c r="E66" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F66" s="99">
-        <v>2020</v>
+      <c r="F66" s="22">
+        <v>2010</v>
       </c>
       <c r="G66" s="32">
         <v>17784.624968178334</v>
       </c>
-      <c r="H66" s="32"/>
+      <c r="H66" s="32">
+        <v>19000.971441364316</v>
+      </c>
       <c r="I66" s="32"/>
       <c r="J66" s="32"/>
       <c r="K66" s="32">
-        <v>18984.970058542225</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="60">
+        <v>19128.959956468352</v>
+      </c>
+      <c r="L66" s="32">
+        <v>20583.516339027319</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="60">
       <c r="A67" t="s">
         <v>165</v>
       </c>
@@ -29602,20 +29870,25 @@
       <c r="E67" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F67" s="99">
-        <v>2020</v>
+      <c r="F67" s="22">
+        <v>2010</v>
       </c>
       <c r="G67" s="32">
         <v>3246.630374582594</v>
       </c>
-      <c r="H67" s="32"/>
+      <c r="H67" s="32">
+        <v>3258.580106471471</v>
+      </c>
       <c r="I67" s="32"/>
       <c r="J67" s="32"/>
       <c r="K67" s="32">
         <v>3485.582370151873</v>
       </c>
-    </row>
-    <row r="68" spans="1:11">
+      <c r="L67" s="32">
+        <v>3558.5479095109677</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68" t="s">
         <v>166</v>
       </c>
@@ -29631,20 +29904,25 @@
       <c r="E68" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F68" s="99">
-        <v>2020</v>
+      <c r="F68" s="22">
+        <v>2010</v>
       </c>
       <c r="G68" s="32">
         <v>213405.25024035602</v>
       </c>
-      <c r="H68" s="32"/>
+      <c r="H68" s="32">
+        <v>213053.72598648595</v>
+      </c>
       <c r="I68" s="32"/>
       <c r="J68" s="32"/>
       <c r="K68" s="32">
-        <v>228514.34195737322</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+        <v>228569.56195737299</v>
+      </c>
+      <c r="L68" s="32">
+        <v>228630.48990387117</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" s="78" t="s">
         <v>378</v>
       </c>
